--- a/Result/profitability/6243.xlsx
+++ b/Result/profitability/6243.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.02</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.03500000000000002</v>
+        <v>-0.14</v>
       </c>
       <c r="N2" t="n">
-        <v>42.36125</v>
+        <v>42.84375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.85</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08999999999999998</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>41.4975</v>
+        <v>41.67249999999999</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.73</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1275</v>
+        <v>-0.035</v>
       </c>
       <c r="N4" t="n">
-        <v>40.9225</v>
+        <v>40.77</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.02</v>
       </c>
       <c r="M5" t="n">
-        <v>0.08624999999999997</v>
+        <v>0.04624999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>40.2675</v>
+        <v>39.79875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.33</v>
       </c>
       <c r="M6" t="n">
-        <v>0.21125</v>
+        <v>0.08124999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>39.4775</v>
+        <v>39.11624999999999</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.33</v>
       </c>
       <c r="M7" t="n">
-        <v>0.24625</v>
+        <v>0.1475</v>
       </c>
       <c r="N7" t="n">
-        <v>38.43125</v>
+        <v>38.23375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.71</v>
       </c>
       <c r="M8" t="n">
-        <v>0.36</v>
+        <v>0.24</v>
       </c>
       <c r="N8" t="n">
-        <v>37.885</v>
+        <v>35.47875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6243</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>78</v>
+      </c>
+      <c r="D75" t="n">
+        <v>47</v>
+      </c>
+      <c r="E75" t="n">
+        <v>32</v>
+      </c>
+      <c r="F75" t="n">
+        <v>40.51</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-40</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-51.21%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-43</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-45</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.15625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>43.43875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="X75" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-19.25</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.3221218206157965</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.4776119402985073</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.08472661545413462</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
